--- a/tame_output/ON/bt/strategyON_20240228.xlsx
+++ b/tame_output/ON/bt/strategyON_20240228.xlsx
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178247</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006537</v>
+        <v>3.305849539006536</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>1.393246578728295</v>
+        <v>1.393430039416235</v>
       </c>
       <c r="E1887" t="n">
-        <v>3.721211491416377</v>
+        <v>3.721284875691553</v>
       </c>
       <c r="F1887" t="n">
         <v>2.293974933993439</v>

--- a/tame_output/ON/bt/strategyON_20240228.xlsx
+++ b/tame_output/ON/bt/strategyON_20240228.xlsx
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.31513067441488</v>
+        <v>3.315130674414879</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>1.393430039416235</v>
+        <v>1.393779303809615</v>
       </c>
       <c r="E1887" t="n">
-        <v>3.721284875691553</v>
+        <v>3.721424581448906</v>
       </c>
       <c r="F1887" t="n">
         <v>2.293974933993439</v>

--- a/tame_output/ON/bt/strategyON_20240228.xlsx
+++ b/tame_output/ON/bt/strategyON_20240228.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.7%</t>
+          <t>448.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-38.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-10.6%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.315130674414879</v>
+        <v>3.31513067441488</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>1.393779303809615</v>
+        <v>1.231699390752594</v>
       </c>
       <c r="E1887" t="n">
-        <v>3.721424581448906</v>
+        <v>3.656592616226097</v>
       </c>
       <c r="F1887" t="n">
         <v>2.293974933993439</v>

--- a/tame_output/ON/bt/strategyON_20240228.xlsx
+++ b/tame_output/ON/bt/strategyON_20240228.xlsx
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.31513067441488</v>
+        <v>3.315130674414879</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
